--- a/verification/cases/roundtrip/bg_color_ranges/init.xlsx
+++ b/verification/cases/roundtrip/bg_color_ranges/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/cells/testdata/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A9D475-C375-6641-B32B-952015AA65C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E067F200-8B37-4C5B-A6CE-66622E0CB349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5120" yWindow="6100" windowWidth="28040" windowHeight="17440" xr2:uid="{9F2350D8-FD8E-9649-B301-70207D66CDF7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F2350D8-FD8E-9649-B301-70207D66CDF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -437,27 +437,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCC7C0A-2886-9440-853C-6A80F3166829}">
   <dimension ref="C4:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2"/>
@@ -465,7 +465,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="2"/>
@@ -473,7 +473,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2"/>
@@ -481,7 +481,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="2"/>
@@ -489,7 +489,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
@@ -497,7 +497,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
@@ -505,7 +505,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
@@ -513,31 +513,31 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
